--- a/ig/nr-update-FrAddress/CodeSystem-fr-core-type-organisation.xlsx
+++ b/ig/nr-update-FrAddress/CodeSystem-fr-core-type-organisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T08:20:44+00:00</t>
+    <t>2023-10-16T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
